--- a/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
+++ b/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="R0353f86735be40b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="R22ecf8e8e44e49dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,17 +55,17 @@
     <x:row r="2">
       <x:c r="A2" t="inlineStr">
         <x:is>
-          <x:t>58-506</x:t>
+          <x:t>15-257</x:t>
         </x:is>
       </x:c>
       <x:c r="B2" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="C2" t="inlineStr">
         <x:is>
-          <x:t>Plac św. apostoła Jana</x:t>
+          <x:t>płk. Czesława Hake</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr">
@@ -75,17 +75,17 @@
       </x:c>
       <x:c r="E2" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="F2" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="G2" t="inlineStr">
         <x:is>
-          <x:t>dolnośląskie</x:t>
+          <x:t>podlaskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" t="inlineStr">
@@ -97,17 +97,17 @@
     <x:row r="3">
       <x:c r="A3" t="inlineStr">
         <x:is>
-          <x:t>58-506</x:t>
+          <x:t>15-257</x:t>
         </x:is>
       </x:c>
       <x:c r="B3" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="C3" t="inlineStr">
         <x:is>
-          <x:t>Plac św. apostoła Jana</x:t>
+          <x:t>płk. Czesława Hake</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr">
@@ -117,17 +117,17 @@
       </x:c>
       <x:c r="E3" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="G3" t="inlineStr">
         <x:is>
-          <x:t>dolnośląskie</x:t>
+          <x:t>podlaskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" t="inlineStr">
@@ -139,17 +139,17 @@
     <x:row r="4">
       <x:c r="A4" t="inlineStr">
         <x:is>
-          <x:t>30-198</x:t>
+          <x:t>80-834</x:t>
         </x:is>
       </x:c>
       <x:c r="B4" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="C4" t="inlineStr">
         <x:is>
-          <x:t>mjr Łupaszki</x:t>
+          <x:t>św. Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr">
@@ -159,17 +159,17 @@
       </x:c>
       <x:c r="E4" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="G4" t="inlineStr">
         <x:is>
-          <x:t>małopolskie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr">
@@ -181,17 +181,17 @@
     <x:row r="5">
       <x:c r="A5" t="inlineStr">
         <x:is>
-          <x:t>30-198</x:t>
+          <x:t>80-834</x:t>
         </x:is>
       </x:c>
       <x:c r="B5" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="C5" t="inlineStr">
         <x:is>
-          <x:t>mjr Łupaszki</x:t>
+          <x:t>św. Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr">
@@ -201,17 +201,17 @@
       </x:c>
       <x:c r="E5" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="G5" t="inlineStr">
         <x:is>
-          <x:t>małopolskie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr">
@@ -223,17 +223,17 @@
     <x:row r="6">
       <x:c r="A6" t="inlineStr">
         <x:is>
-          <x:t>48-300</x:t>
+          <x:t>81-577</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Gdynia</x:t>
         </x:is>
       </x:c>
       <x:c r="C6" t="inlineStr">
         <x:is>
-          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+          <x:t>o. Pio</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr">
@@ -243,17 +243,17 @@
       </x:c>
       <x:c r="E6" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Gdynia</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" t="inlineStr">
         <x:is>
-          <x:t>nyski</x:t>
+          <x:t>Gdynia</x:t>
         </x:is>
       </x:c>
       <x:c r="G6" t="inlineStr">
         <x:is>
-          <x:t>opolskie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr">
@@ -265,17 +265,17 @@
     <x:row r="7">
       <x:c r="A7" t="inlineStr">
         <x:is>
-          <x:t>48-300</x:t>
+          <x:t>81-577</x:t>
         </x:is>
       </x:c>
       <x:c r="B7" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Gdynia</x:t>
         </x:is>
       </x:c>
       <x:c r="C7" t="inlineStr">
         <x:is>
-          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+          <x:t>o. Pio</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr">
@@ -285,17 +285,17 @@
       </x:c>
       <x:c r="E7" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Gdynia</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" t="inlineStr">
         <x:is>
-          <x:t>nyski</x:t>
+          <x:t>Gdynia</x:t>
         </x:is>
       </x:c>
       <x:c r="G7" t="inlineStr">
         <x:is>
-          <x:t>opolskie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr">
@@ -307,17 +307,17 @@
     <x:row r="8">
       <x:c r="A8" t="inlineStr">
         <x:is>
-          <x:t>71-602</x:t>
+          <x:t>58-506</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="C8" t="inlineStr">
         <x:is>
-          <x:t>Storrady-Świętosławy</x:t>
+          <x:t>Plac św. apostoła Jana</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr">
@@ -327,17 +327,17 @@
       </x:c>
       <x:c r="E8" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="G8" t="inlineStr">
         <x:is>
-          <x:t>zachodniopomorskie</x:t>
+          <x:t>dolnośląskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr">
@@ -349,17 +349,17 @@
     <x:row r="9">
       <x:c r="A9" t="inlineStr">
         <x:is>
-          <x:t>71-602</x:t>
+          <x:t>58-506</x:t>
         </x:is>
       </x:c>
       <x:c r="B9" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="C9" t="inlineStr">
         <x:is>
-          <x:t>Storrady-Świętosławy</x:t>
+          <x:t>Plac św. apostoła Jana</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr">
@@ -369,17 +369,17 @@
       </x:c>
       <x:c r="E9" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="G9" t="inlineStr">
         <x:is>
-          <x:t>zachodniopomorskie</x:t>
+          <x:t>dolnośląskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr">
@@ -391,17 +391,17 @@
     <x:row r="10">
       <x:c r="A10" t="inlineStr">
         <x:is>
-          <x:t>43-100</x:t>
+          <x:t>46-200</x:t>
         </x:is>
       </x:c>
       <x:c r="B10" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>Kluczbork</x:t>
         </x:is>
       </x:c>
       <x:c r="C10" t="inlineStr">
         <x:is>
-          <x:t>van Beethovena</x:t>
+          <x:t>Generała Bema</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr">
@@ -411,17 +411,17 @@
       </x:c>
       <x:c r="E10" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>Kluczbork</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>kluczborski</x:t>
         </x:is>
       </x:c>
       <x:c r="G10" t="inlineStr">
         <x:is>
-          <x:t>śląskie</x:t>
+          <x:t>opolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr">
@@ -433,17 +433,17 @@
     <x:row r="11">
       <x:c r="A11" t="inlineStr">
         <x:is>
-          <x:t>43-100</x:t>
+          <x:t>46-200</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>Kluczbork</x:t>
         </x:is>
       </x:c>
       <x:c r="C11" t="inlineStr">
         <x:is>
-          <x:t>van Beethovena</x:t>
+          <x:t>Generała Bema</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr">
@@ -453,17 +453,17 @@
       </x:c>
       <x:c r="E11" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>Kluczbork</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>kluczborski</x:t>
         </x:is>
       </x:c>
       <x:c r="G11" t="inlineStr">
         <x:is>
-          <x:t>śląskie</x:t>
+          <x:t>opolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr">
@@ -475,17 +475,17 @@
     <x:row r="12">
       <x:c r="A12" t="inlineStr">
         <x:is>
-          <x:t>66-006</x:t>
+          <x:t>91-492</x:t>
         </x:is>
       </x:c>
       <x:c r="B12" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>Łódź</x:t>
         </x:is>
       </x:c>
       <x:c r="C12" t="inlineStr">
         <x:is>
-          <x:t>Ochla-Osiedle Dworskie</x:t>
+          <x:t>Generała Bema</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr">
@@ -495,17 +495,17 @@
       </x:c>
       <x:c r="E12" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>Łódź</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>Łódź</x:t>
         </x:is>
       </x:c>
       <x:c r="G12" t="inlineStr">
         <x:is>
-          <x:t>lubuskie</x:t>
+          <x:t>łódzkie</x:t>
         </x:is>
       </x:c>
       <x:c r="H12" t="inlineStr">
@@ -517,40 +517,712 @@
     <x:row r="13">
       <x:c r="A13" t="inlineStr">
         <x:is>
+          <x:t>91-492</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" t="inlineStr">
+        <x:is>
+          <x:t>Łódź</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" t="inlineStr">
+        <x:is>
+          <x:t>Generała Bema</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E13" t="inlineStr">
+        <x:is>
+          <x:t>Łódź</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" t="inlineStr">
+        <x:is>
+          <x:t>Łódź</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G13" t="inlineStr">
+        <x:is>
+          <x:t>łódzkie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H13" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="inlineStr">
+        <x:is>
+          <x:t>48-300</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" t="inlineStr">
+        <x:is>
+          <x:t>Nysa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" t="inlineStr">
+        <x:is>
+          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E14" t="inlineStr">
+        <x:is>
+          <x:t>Nysa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" t="inlineStr">
+        <x:is>
+          <x:t>nyski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G14" t="inlineStr">
+        <x:is>
+          <x:t>opolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H14" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="inlineStr">
+        <x:is>
+          <x:t>48-300</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" t="inlineStr">
+        <x:is>
+          <x:t>Nysa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" t="inlineStr">
+        <x:is>
+          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E15" t="inlineStr">
+        <x:is>
+          <x:t>Nysa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" t="inlineStr">
+        <x:is>
+          <x:t>nyski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G15" t="inlineStr">
+        <x:is>
+          <x:t>opolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H15" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="inlineStr">
+        <x:is>
+          <x:t>42-256</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" t="inlineStr">
+        <x:is>
+          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E16" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" t="inlineStr">
+        <x:is>
+          <x:t>częstochowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G16" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H16" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="inlineStr">
+        <x:is>
+          <x:t>42-256</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" t="inlineStr">
+        <x:is>
+          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E17" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" t="inlineStr">
+        <x:is>
+          <x:t>częstochowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G17" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H17" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="inlineStr">
+        <x:is>
+          <x:t>71-602</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" t="inlineStr">
+        <x:is>
+          <x:t>Storrady-Świętosławy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E18" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F18" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G18" t="inlineStr">
+        <x:is>
+          <x:t>zachodniopomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H18" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="inlineStr">
+        <x:is>
+          <x:t>71-602</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" t="inlineStr">
+        <x:is>
+          <x:t>Storrady-Świętosławy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E19" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F19" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G19" t="inlineStr">
+        <x:is>
+          <x:t>zachodniopomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H19" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="inlineStr">
+        <x:is>
+          <x:t>43-100</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" t="inlineStr">
+        <x:is>
+          <x:t>Tychy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" t="inlineStr">
+        <x:is>
+          <x:t>van Beethovena</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E20" t="inlineStr">
+        <x:is>
+          <x:t>Tychy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F20" t="inlineStr">
+        <x:is>
+          <x:t>Tychy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G20" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H20" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="inlineStr">
+        <x:is>
+          <x:t>43-100</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" t="inlineStr">
+        <x:is>
+          <x:t>Tychy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" t="inlineStr">
+        <x:is>
+          <x:t>van Beethovena</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E21" t="inlineStr">
+        <x:is>
+          <x:t>Tychy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F21" t="inlineStr">
+        <x:is>
+          <x:t>Tychy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G21" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H21" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="inlineStr">
+        <x:is>
+          <x:t>03-264</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" t="inlineStr">
+        <x:is>
+          <x:t>Ojca Aniceta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E22" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F22" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G22" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H22" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="inlineStr">
+        <x:is>
+          <x:t>03-264</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" t="inlineStr">
+        <x:is>
+          <x:t>Ojca Aniceta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E23" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F23" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G23" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H23" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="inlineStr">
+        <x:is>
+          <x:t>50-153</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" t="inlineStr">
+        <x:is>
+          <x:t>św. Ducha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E24" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F24" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G24" t="inlineStr">
+        <x:is>
+          <x:t>dolnośląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H24" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="inlineStr">
+        <x:is>
+          <x:t>50-153</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" t="inlineStr">
+        <x:is>
+          <x:t>św. Ducha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D25" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E25" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F25" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G25" t="inlineStr">
+        <x:is>
+          <x:t>dolnośląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H25" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="inlineStr">
+        <x:is>
+          <x:t>65-088</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B26" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C26" t="inlineStr">
+        <x:is>
+          <x:t>Baudouina</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E26" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F26" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G26" t="inlineStr">
+        <x:is>
+          <x:t>lubuskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H26" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="inlineStr">
+        <x:is>
+          <x:t>65-088</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" t="inlineStr">
+        <x:is>
+          <x:t>Baudouina</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E27" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F27" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G27" t="inlineStr">
+        <x:is>
+          <x:t>lubuskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H27" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="inlineStr">
+        <x:is>
           <x:t>66-006</x:t>
         </x:is>
       </x:c>
-      <x:c r="B13" t="inlineStr">
+      <x:c r="B28" t="inlineStr">
         <x:is>
           <x:t>Zielona Góra</x:t>
         </x:is>
       </x:c>
-      <x:c r="C13" t="inlineStr">
+      <x:c r="C28" t="inlineStr">
         <x:is>
           <x:t>Ochla-Osiedle Dworskie</x:t>
         </x:is>
       </x:c>
-      <x:c r="D13" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="E13" t="inlineStr">
+      <x:c r="D28" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E28" t="inlineStr">
         <x:is>
           <x:t>Zielona Góra</x:t>
         </x:is>
       </x:c>
-      <x:c r="F13" t="inlineStr">
+      <x:c r="F28" t="inlineStr">
         <x:is>
           <x:t>Zielona Góra</x:t>
         </x:is>
       </x:c>
-      <x:c r="G13" t="inlineStr">
+      <x:c r="G28" t="inlineStr">
         <x:is>
           <x:t>lubuskie</x:t>
         </x:is>
       </x:c>
-      <x:c r="H13" t="inlineStr">
+      <x:c r="H28" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="inlineStr">
+        <x:is>
+          <x:t>66-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" t="inlineStr">
+        <x:is>
+          <x:t>Ochla-Osiedle Dworskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E29" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F29" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G29" t="inlineStr">
+        <x:is>
+          <x:t>lubuskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H29" t="inlineStr">
         <x:is>
           <x:t/>
         </x:is>

--- a/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
+++ b/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="R22ecf8e8e44e49dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="Rfbd3f139fda64c24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,7 +55,7 @@
     <x:row r="2">
       <x:c r="A2" t="inlineStr">
         <x:is>
-          <x:t>15-257</x:t>
+          <x:t>15-092</x:t>
         </x:is>
       </x:c>
       <x:c r="B2" t="inlineStr">
@@ -65,7 +65,7 @@
       </x:c>
       <x:c r="C2" t="inlineStr">
         <x:is>
-          <x:t>płk. Czesława Hake</x:t>
+          <x:t>Kapitana Wojska Polskiego Weroniki Topór</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr">
@@ -97,7 +97,7 @@
     <x:row r="3">
       <x:c r="A3" t="inlineStr">
         <x:is>
-          <x:t>15-257</x:t>
+          <x:t>15-092</x:t>
         </x:is>
       </x:c>
       <x:c r="B3" t="inlineStr">
@@ -107,7 +107,7 @@
       </x:c>
       <x:c r="C3" t="inlineStr">
         <x:is>
-          <x:t>płk. Czesława Hake</x:t>
+          <x:t>Kapitana Wojska Polskiego Weroniki Topór</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr">
@@ -139,17 +139,17 @@
     <x:row r="4">
       <x:c r="A4" t="inlineStr">
         <x:is>
-          <x:t>80-834</x:t>
+          <x:t>15-204</x:t>
         </x:is>
       </x:c>
       <x:c r="B4" t="inlineStr">
         <x:is>
-          <x:t>Gdańsk</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="C4" t="inlineStr">
         <x:is>
-          <x:t>św. Ducha</x:t>
+          <x:t>pl. świętego Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr">
@@ -159,17 +159,17 @@
       </x:c>
       <x:c r="E4" t="inlineStr">
         <x:is>
-          <x:t>Gdańsk</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" t="inlineStr">
         <x:is>
-          <x:t>Gdańsk</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="G4" t="inlineStr">
         <x:is>
-          <x:t>pomorskie</x:t>
+          <x:t>podlaskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr">
@@ -181,17 +181,17 @@
     <x:row r="5">
       <x:c r="A5" t="inlineStr">
         <x:is>
-          <x:t>80-834</x:t>
+          <x:t>15-204</x:t>
         </x:is>
       </x:c>
       <x:c r="B5" t="inlineStr">
         <x:is>
-          <x:t>Gdańsk</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="C5" t="inlineStr">
         <x:is>
-          <x:t>św. Ducha</x:t>
+          <x:t>pl. świętego Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr">
@@ -201,17 +201,17 @@
       </x:c>
       <x:c r="E5" t="inlineStr">
         <x:is>
-          <x:t>Gdańsk</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" t="inlineStr">
         <x:is>
-          <x:t>Gdańsk</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="G5" t="inlineStr">
         <x:is>
-          <x:t>pomorskie</x:t>
+          <x:t>podlaskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr">
@@ -223,17 +223,17 @@
     <x:row r="6">
       <x:c r="A6" t="inlineStr">
         <x:is>
-          <x:t>81-577</x:t>
+          <x:t>43-300</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" t="inlineStr">
         <x:is>
-          <x:t>Gdynia</x:t>
+          <x:t>Bielsko-Biała</x:t>
         </x:is>
       </x:c>
       <x:c r="C6" t="inlineStr">
         <x:is>
-          <x:t>o. Pio</x:t>
+          <x:t>św. Trójcy</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr">
@@ -243,17 +243,17 @@
       </x:c>
       <x:c r="E6" t="inlineStr">
         <x:is>
-          <x:t>Gdynia</x:t>
+          <x:t>Bielsko-Biała</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" t="inlineStr">
         <x:is>
-          <x:t>Gdynia</x:t>
+          <x:t>Bielsko-Biała</x:t>
         </x:is>
       </x:c>
       <x:c r="G6" t="inlineStr">
         <x:is>
-          <x:t>pomorskie</x:t>
+          <x:t>śląskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr">
@@ -265,17 +265,17 @@
     <x:row r="7">
       <x:c r="A7" t="inlineStr">
         <x:is>
-          <x:t>81-577</x:t>
+          <x:t>43-300</x:t>
         </x:is>
       </x:c>
       <x:c r="B7" t="inlineStr">
         <x:is>
-          <x:t>Gdynia</x:t>
+          <x:t>Bielsko-Biała</x:t>
         </x:is>
       </x:c>
       <x:c r="C7" t="inlineStr">
         <x:is>
-          <x:t>o. Pio</x:t>
+          <x:t>św. Trójcy</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr">
@@ -285,17 +285,17 @@
       </x:c>
       <x:c r="E7" t="inlineStr">
         <x:is>
-          <x:t>Gdynia</x:t>
+          <x:t>Bielsko-Biała</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" t="inlineStr">
         <x:is>
-          <x:t>Gdynia</x:t>
+          <x:t>Bielsko-Biała</x:t>
         </x:is>
       </x:c>
       <x:c r="G7" t="inlineStr">
         <x:is>
-          <x:t>pomorskie</x:t>
+          <x:t>śląskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr">
@@ -307,17 +307,17 @@
     <x:row r="8">
       <x:c r="A8" t="inlineStr">
         <x:is>
-          <x:t>58-506</x:t>
+          <x:t>85-143</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="C8" t="inlineStr">
         <x:is>
-          <x:t>Plac św. apostoła Jana</x:t>
+          <x:t>świętego Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr">
@@ -327,17 +327,17 @@
       </x:c>
       <x:c r="E8" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="G8" t="inlineStr">
         <x:is>
-          <x:t>dolnośląskie</x:t>
+          <x:t>kujawsko-pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr">
@@ -349,17 +349,17 @@
     <x:row r="9">
       <x:c r="A9" t="inlineStr">
         <x:is>
-          <x:t>58-506</x:t>
+          <x:t>85-143</x:t>
         </x:is>
       </x:c>
       <x:c r="B9" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="C9" t="inlineStr">
         <x:is>
-          <x:t>Plac św. apostoła Jana</x:t>
+          <x:t>świętego Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr">
@@ -369,17 +369,17 @@
       </x:c>
       <x:c r="E9" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" t="inlineStr">
         <x:is>
-          <x:t>Jelenia Góra</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="G9" t="inlineStr">
         <x:is>
-          <x:t>dolnośląskie</x:t>
+          <x:t>kujawsko-pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr">
@@ -391,17 +391,17 @@
     <x:row r="10">
       <x:c r="A10" t="inlineStr">
         <x:is>
-          <x:t>46-200</x:t>
+          <x:t>85-224</x:t>
         </x:is>
       </x:c>
       <x:c r="B10" t="inlineStr">
         <x:is>
-          <x:t>Kluczbork</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="C10" t="inlineStr">
         <x:is>
-          <x:t>Generała Bema</x:t>
+          <x:t>św. Trójcy</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr">
@@ -411,17 +411,17 @@
       </x:c>
       <x:c r="E10" t="inlineStr">
         <x:is>
-          <x:t>Kluczbork</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" t="inlineStr">
         <x:is>
-          <x:t>kluczborski</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="G10" t="inlineStr">
         <x:is>
-          <x:t>opolskie</x:t>
+          <x:t>kujawsko-pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr">
@@ -433,17 +433,17 @@
     <x:row r="11">
       <x:c r="A11" t="inlineStr">
         <x:is>
-          <x:t>46-200</x:t>
+          <x:t>85-224</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" t="inlineStr">
         <x:is>
-          <x:t>Kluczbork</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="C11" t="inlineStr">
         <x:is>
-          <x:t>Generała Bema</x:t>
+          <x:t>św. Trójcy</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr">
@@ -453,17 +453,17 @@
       </x:c>
       <x:c r="E11" t="inlineStr">
         <x:is>
-          <x:t>Kluczbork</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" t="inlineStr">
         <x:is>
-          <x:t>kluczborski</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="G11" t="inlineStr">
         <x:is>
-          <x:t>opolskie</x:t>
+          <x:t>kujawsko-pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr">
@@ -475,17 +475,17 @@
     <x:row r="12">
       <x:c r="A12" t="inlineStr">
         <x:is>
-          <x:t>91-492</x:t>
+          <x:t>89-600</x:t>
         </x:is>
       </x:c>
       <x:c r="B12" t="inlineStr">
         <x:is>
-          <x:t>Łódź</x:t>
+          <x:t>Chojnice</x:t>
         </x:is>
       </x:c>
       <x:c r="C12" t="inlineStr">
         <x:is>
-          <x:t>Generała Bema</x:t>
+          <x:t>świętego Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr">
@@ -495,17 +495,17 @@
       </x:c>
       <x:c r="E12" t="inlineStr">
         <x:is>
-          <x:t>Łódź</x:t>
+          <x:t>Chojnice</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" t="inlineStr">
         <x:is>
-          <x:t>Łódź</x:t>
+          <x:t>chojnicki</x:t>
         </x:is>
       </x:c>
       <x:c r="G12" t="inlineStr">
         <x:is>
-          <x:t>łódzkie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H12" t="inlineStr">
@@ -517,17 +517,17 @@
     <x:row r="13">
       <x:c r="A13" t="inlineStr">
         <x:is>
-          <x:t>91-492</x:t>
+          <x:t>89-600</x:t>
         </x:is>
       </x:c>
       <x:c r="B13" t="inlineStr">
         <x:is>
-          <x:t>Łódź</x:t>
+          <x:t>Chojnice</x:t>
         </x:is>
       </x:c>
       <x:c r="C13" t="inlineStr">
         <x:is>
-          <x:t>Generała Bema</x:t>
+          <x:t>świętego Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" t="inlineStr">
@@ -537,17 +537,17 @@
       </x:c>
       <x:c r="E13" t="inlineStr">
         <x:is>
-          <x:t>Łódź</x:t>
+          <x:t>Chojnice</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" t="inlineStr">
         <x:is>
-          <x:t>Łódź</x:t>
+          <x:t>chojnicki</x:t>
         </x:is>
       </x:c>
       <x:c r="G13" t="inlineStr">
         <x:is>
-          <x:t>łódzkie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H13" t="inlineStr">
@@ -559,17 +559,17 @@
     <x:row r="14">
       <x:c r="A14" t="inlineStr">
         <x:is>
-          <x:t>48-300</x:t>
+          <x:t>80-834</x:t>
         </x:is>
       </x:c>
       <x:c r="B14" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="C14" t="inlineStr">
         <x:is>
-          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+          <x:t>św. Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D14" t="inlineStr">
@@ -579,17 +579,17 @@
       </x:c>
       <x:c r="E14" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="F14" t="inlineStr">
         <x:is>
-          <x:t>nyski</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="G14" t="inlineStr">
         <x:is>
-          <x:t>opolskie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H14" t="inlineStr">
@@ -601,17 +601,17 @@
     <x:row r="15">
       <x:c r="A15" t="inlineStr">
         <x:is>
-          <x:t>48-300</x:t>
+          <x:t>80-834</x:t>
         </x:is>
       </x:c>
       <x:c r="B15" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="C15" t="inlineStr">
         <x:is>
-          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+          <x:t>św. Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D15" t="inlineStr">
@@ -621,17 +621,17 @@
       </x:c>
       <x:c r="E15" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="F15" t="inlineStr">
         <x:is>
-          <x:t>nyski</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="G15" t="inlineStr">
         <x:is>
-          <x:t>opolskie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H15" t="inlineStr">
@@ -643,17 +643,17 @@
     <x:row r="16">
       <x:c r="A16" t="inlineStr">
         <x:is>
-          <x:t>42-256</x:t>
+          <x:t>80-822</x:t>
         </x:is>
       </x:c>
       <x:c r="B16" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" t="inlineStr">
         <x:is>
-          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+          <x:t>św. Trójcy</x:t>
         </x:is>
       </x:c>
       <x:c r="D16" t="inlineStr">
@@ -663,17 +663,17 @@
       </x:c>
       <x:c r="E16" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" t="inlineStr">
         <x:is>
-          <x:t>częstochowski</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="G16" t="inlineStr">
         <x:is>
-          <x:t>śląskie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H16" t="inlineStr">
@@ -685,17 +685,17 @@
     <x:row r="17">
       <x:c r="A17" t="inlineStr">
         <x:is>
-          <x:t>42-256</x:t>
+          <x:t>80-822</x:t>
         </x:is>
       </x:c>
       <x:c r="B17" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="C17" t="inlineStr">
         <x:is>
-          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+          <x:t>św. Trójcy</x:t>
         </x:is>
       </x:c>
       <x:c r="D17" t="inlineStr">
@@ -705,17 +705,17 @@
       </x:c>
       <x:c r="E17" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="F17" t="inlineStr">
         <x:is>
-          <x:t>częstochowski</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="G17" t="inlineStr">
         <x:is>
-          <x:t>śląskie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H17" t="inlineStr">
@@ -727,17 +727,17 @@
     <x:row r="18">
       <x:c r="A18" t="inlineStr">
         <x:is>
-          <x:t>71-602</x:t>
+          <x:t>58-506</x:t>
         </x:is>
       </x:c>
       <x:c r="B18" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="C18" t="inlineStr">
         <x:is>
-          <x:t>Storrady-Świętosławy</x:t>
+          <x:t>Plac św. apostoła Jana</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" t="inlineStr">
@@ -747,17 +747,17 @@
       </x:c>
       <x:c r="E18" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="G18" t="inlineStr">
         <x:is>
-          <x:t>zachodniopomorskie</x:t>
+          <x:t>dolnośląskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H18" t="inlineStr">
@@ -769,17 +769,17 @@
     <x:row r="19">
       <x:c r="A19" t="inlineStr">
         <x:is>
-          <x:t>71-602</x:t>
+          <x:t>58-506</x:t>
         </x:is>
       </x:c>
       <x:c r="B19" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="C19" t="inlineStr">
         <x:is>
-          <x:t>Storrady-Świętosławy</x:t>
+          <x:t>Plac św. apostoła Jana</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" t="inlineStr">
@@ -789,17 +789,17 @@
       </x:c>
       <x:c r="E19" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Jelenia Góra</x:t>
         </x:is>
       </x:c>
       <x:c r="G19" t="inlineStr">
         <x:is>
-          <x:t>zachodniopomorskie</x:t>
+          <x:t>dolnośląskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H19" t="inlineStr">
@@ -811,17 +811,17 @@
     <x:row r="20">
       <x:c r="A20" t="inlineStr">
         <x:is>
-          <x:t>43-100</x:t>
+          <x:t>31-812</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="C20" t="inlineStr">
         <x:is>
-          <x:t>van Beethovena</x:t>
+          <x:t>Świętej Rodziny</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" t="inlineStr">
@@ -831,17 +831,17 @@
       </x:c>
       <x:c r="E20" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="G20" t="inlineStr">
         <x:is>
-          <x:t>śląskie</x:t>
+          <x:t>małopolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H20" t="inlineStr">
@@ -853,17 +853,17 @@
     <x:row r="21">
       <x:c r="A21" t="inlineStr">
         <x:is>
-          <x:t>43-100</x:t>
+          <x:t>31-812</x:t>
         </x:is>
       </x:c>
       <x:c r="B21" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="C21" t="inlineStr">
         <x:is>
-          <x:t>van Beethovena</x:t>
+          <x:t>Świętej Rodziny</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" t="inlineStr">
@@ -873,17 +873,17 @@
       </x:c>
       <x:c r="E21" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" t="inlineStr">
         <x:is>
-          <x:t>Tychy</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="G21" t="inlineStr">
         <x:is>
-          <x:t>śląskie</x:t>
+          <x:t>małopolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H21" t="inlineStr">
@@ -895,17 +895,17 @@
     <x:row r="22">
       <x:c r="A22" t="inlineStr">
         <x:is>
-          <x:t>03-264</x:t>
+          <x:t>31-023</x:t>
         </x:is>
       </x:c>
       <x:c r="B22" t="inlineStr">
         <x:is>
-          <x:t>Warszawa</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="C22" t="inlineStr">
         <x:is>
-          <x:t>Ojca Aniceta</x:t>
+          <x:t>Plac Świętego Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" t="inlineStr">
@@ -915,17 +915,17 @@
       </x:c>
       <x:c r="E22" t="inlineStr">
         <x:is>
-          <x:t>Warszawa</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" t="inlineStr">
         <x:is>
-          <x:t>Warszawa</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="G22" t="inlineStr">
         <x:is>
-          <x:t>mazowieckie</x:t>
+          <x:t>małopolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H22" t="inlineStr">
@@ -937,17 +937,17 @@
     <x:row r="23">
       <x:c r="A23" t="inlineStr">
         <x:is>
-          <x:t>03-264</x:t>
+          <x:t>31-023</x:t>
         </x:is>
       </x:c>
       <x:c r="B23" t="inlineStr">
         <x:is>
-          <x:t>Warszawa</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="C23" t="inlineStr">
         <x:is>
-          <x:t>Ojca Aniceta</x:t>
+          <x:t>Plac Świętego Ducha</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" t="inlineStr">
@@ -957,17 +957,17 @@
       </x:c>
       <x:c r="E23" t="inlineStr">
         <x:is>
-          <x:t>Warszawa</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" t="inlineStr">
         <x:is>
-          <x:t>Warszawa</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="G23" t="inlineStr">
         <x:is>
-          <x:t>mazowieckie</x:t>
+          <x:t>małopolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H23" t="inlineStr">
@@ -979,37 +979,37 @@
     <x:row r="24">
       <x:c r="A24" t="inlineStr">
         <x:is>
-          <x:t>50-153</x:t>
+          <x:t>31-028</x:t>
         </x:is>
       </x:c>
       <x:c r="B24" t="inlineStr">
         <x:is>
-          <x:t>Wrocław</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="C24" t="inlineStr">
         <x:is>
-          <x:t>św. Ducha</x:t>
+          <x:t>Świętego Krzyża</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>1-15</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" t="inlineStr">
         <x:is>
-          <x:t>Wrocław</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" t="inlineStr">
         <x:is>
-          <x:t>Wrocław</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="G24" t="inlineStr">
         <x:is>
-          <x:t>dolnośląskie</x:t>
+          <x:t>małopolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H24" t="inlineStr">
@@ -1021,37 +1021,37 @@
     <x:row r="25">
       <x:c r="A25" t="inlineStr">
         <x:is>
-          <x:t>50-153</x:t>
+          <x:t>31-028</x:t>
         </x:is>
       </x:c>
       <x:c r="B25" t="inlineStr">
         <x:is>
-          <x:t>Wrocław</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="C25" t="inlineStr">
         <x:is>
-          <x:t>św. Ducha</x:t>
+          <x:t>Świętego Krzyża</x:t>
         </x:is>
       </x:c>
       <x:c r="D25" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>1-15</x:t>
         </x:is>
       </x:c>
       <x:c r="E25" t="inlineStr">
         <x:is>
-          <x:t>Wrocław</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" t="inlineStr">
         <x:is>
-          <x:t>Wrocław</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="G25" t="inlineStr">
         <x:is>
-          <x:t>dolnośląskie</x:t>
+          <x:t>małopolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H25" t="inlineStr">
@@ -1063,37 +1063,37 @@
     <x:row r="26">
       <x:c r="A26" t="inlineStr">
         <x:is>
-          <x:t>65-088</x:t>
+          <x:t>31-023</x:t>
         </x:is>
       </x:c>
       <x:c r="B26" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="C26" t="inlineStr">
         <x:is>
-          <x:t>Baudouina</x:t>
+          <x:t>Świętego Krzyża</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>16-DK(p)</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="G26" t="inlineStr">
         <x:is>
-          <x:t>lubuskie</x:t>
+          <x:t>małopolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" t="inlineStr">
@@ -1105,37 +1105,37 @@
     <x:row r="27">
       <x:c r="A27" t="inlineStr">
         <x:is>
-          <x:t>65-088</x:t>
+          <x:t>31-023</x:t>
         </x:is>
       </x:c>
       <x:c r="B27" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="C27" t="inlineStr">
         <x:is>
-          <x:t>Baudouina</x:t>
+          <x:t>Świętego Krzyża</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>16-DK(p)</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>Kraków</x:t>
         </x:is>
       </x:c>
       <x:c r="G27" t="inlineStr">
         <x:is>
-          <x:t>lubuskie</x:t>
+          <x:t>małopolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H27" t="inlineStr">
@@ -1147,17 +1147,17 @@
     <x:row r="28">
       <x:c r="A28" t="inlineStr">
         <x:is>
-          <x:t>66-006</x:t>
+          <x:t>48-300</x:t>
         </x:is>
       </x:c>
       <x:c r="B28" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>Nysa</x:t>
         </x:is>
       </x:c>
       <x:c r="C28" t="inlineStr">
         <x:is>
-          <x:t>Ochla-Osiedle Dworskie</x:t>
+          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" t="inlineStr">
@@ -1167,17 +1167,17 @@
       </x:c>
       <x:c r="E28" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>Nysa</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" t="inlineStr">
         <x:is>
-          <x:t>Zielona Góra</x:t>
+          <x:t>nyski</x:t>
         </x:is>
       </x:c>
       <x:c r="G28" t="inlineStr">
         <x:is>
-          <x:t>lubuskie</x:t>
+          <x:t>opolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H28" t="inlineStr">
@@ -1189,40 +1189,1636 @@
     <x:row r="29">
       <x:c r="A29" t="inlineStr">
         <x:is>
-          <x:t>66-006</x:t>
+          <x:t>48-300</x:t>
         </x:is>
       </x:c>
       <x:c r="B29" t="inlineStr">
         <x:is>
+          <x:t>Nysa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" t="inlineStr">
+        <x:is>
+          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E29" t="inlineStr">
+        <x:is>
+          <x:t>Nysa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F29" t="inlineStr">
+        <x:is>
+          <x:t>nyski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G29" t="inlineStr">
+        <x:is>
+          <x:t>opolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H29" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="inlineStr">
+        <x:is>
+          <x:t>42-256</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B30" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" t="inlineStr">
+        <x:is>
+          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E30" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F30" t="inlineStr">
+        <x:is>
+          <x:t>częstochowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G30" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H30" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="inlineStr">
+        <x:is>
+          <x:t>42-256</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B31" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C31" t="inlineStr">
+        <x:is>
+          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D31" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E31" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F31" t="inlineStr">
+        <x:is>
+          <x:t>częstochowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G31" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H31" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="inlineStr">
+        <x:is>
+          <x:t>42-256</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" t="inlineStr">
+        <x:is>
+          <x:t>Świętej Puszczy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E32" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" t="inlineStr">
+        <x:is>
+          <x:t>częstochowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G32" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H32" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="inlineStr">
+        <x:is>
+          <x:t>42-256</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C33" t="inlineStr">
+        <x:is>
+          <x:t>Świętej Puszczy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D33" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E33" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F33" t="inlineStr">
+        <x:is>
+          <x:t>częstochowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G33" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H33" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="inlineStr">
+        <x:is>
+          <x:t>07-310</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" t="inlineStr">
+        <x:is>
+          <x:t>Ostrów Mazowiecka</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C34" t="inlineStr">
+        <x:is>
+          <x:t>Spokojna</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E34" t="inlineStr">
+        <x:is>
+          <x:t>Ostrów Mazowiecka</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F34" t="inlineStr">
+        <x:is>
+          <x:t>ostrowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G34" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H34" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="inlineStr">
+        <x:is>
+          <x:t>07-310</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" t="inlineStr">
+        <x:is>
+          <x:t>Ostrów Mazowiecka</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C35" t="inlineStr">
+        <x:is>
+          <x:t>Spokojna</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E35" t="inlineStr">
+        <x:is>
+          <x:t>Ostrów Mazowiecka</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" t="inlineStr">
+        <x:is>
+          <x:t>ostrowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G35" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H35" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="inlineStr">
+        <x:is>
+          <x:t>61-447</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C36" t="inlineStr">
+        <x:is>
+          <x:t>Błogosławionej Poznańskiej Piątki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D36" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E36" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F36" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G36" t="inlineStr">
+        <x:is>
+          <x:t>wielkopolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H36" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="inlineStr">
+        <x:is>
+          <x:t>61-447</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C37" t="inlineStr">
+        <x:is>
+          <x:t>Błogosławionej Poznańskiej Piątki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D37" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E37" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F37" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G37" t="inlineStr">
+        <x:is>
+          <x:t>wielkopolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H37" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="inlineStr">
+        <x:is>
+          <x:t>61-450</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C38" t="inlineStr">
+        <x:is>
+          <x:t>Błogosławionej Poznańskiej Piątki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D38" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E38" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F38" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G38" t="inlineStr">
+        <x:is>
+          <x:t>wielkopolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H38" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="inlineStr">
+        <x:is>
+          <x:t>61-450</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B39" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C39" t="inlineStr">
+        <x:is>
+          <x:t>Błogosławionej Poznańskiej Piątki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D39" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E39" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F39" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G39" t="inlineStr">
+        <x:is>
+          <x:t>wielkopolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H39" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="inlineStr">
+        <x:is>
+          <x:t>61-478</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B40" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C40" t="inlineStr">
+        <x:is>
+          <x:t>św. Trójcy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D40" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E40" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F40" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G40" t="inlineStr">
+        <x:is>
+          <x:t>wielkopolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H40" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="inlineStr">
+        <x:is>
+          <x:t>61-478</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B41" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C41" t="inlineStr">
+        <x:is>
+          <x:t>św. Trójcy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D41" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E41" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F41" t="inlineStr">
+        <x:is>
+          <x:t>Poznań</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G41" t="inlineStr">
+        <x:is>
+          <x:t>wielkopolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H41" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="inlineStr">
+        <x:is>
+          <x:t>35-213</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B42" t="inlineStr">
+        <x:is>
+          <x:t>Rzeszów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C42" t="inlineStr">
+        <x:is>
+          <x:t>Świętej Rodziny</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D42" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E42" t="inlineStr">
+        <x:is>
+          <x:t>Rzeszów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F42" t="inlineStr">
+        <x:is>
+          <x:t>Rzeszów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G42" t="inlineStr">
+        <x:is>
+          <x:t>podkarpackie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H42" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="inlineStr">
+        <x:is>
+          <x:t>35-213</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B43" t="inlineStr">
+        <x:is>
+          <x:t>Rzeszów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C43" t="inlineStr">
+        <x:is>
+          <x:t>Świętej Rodziny</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D43" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E43" t="inlineStr">
+        <x:is>
+          <x:t>Rzeszów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F43" t="inlineStr">
+        <x:is>
+          <x:t>Rzeszów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G43" t="inlineStr">
+        <x:is>
+          <x:t>podkarpackie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H43" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="inlineStr">
+        <x:is>
+          <x:t>73-110</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B44" t="inlineStr">
+        <x:is>
+          <x:t>Stargard</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C44" t="inlineStr">
+        <x:is>
+          <x:t>Plac Świętego Ducha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D44" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E44" t="inlineStr">
+        <x:is>
+          <x:t>Stargard</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F44" t="inlineStr">
+        <x:is>
+          <x:t>stargardzki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G44" t="inlineStr">
+        <x:is>
+          <x:t>zachodniopomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H44" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="inlineStr">
+        <x:is>
+          <x:t>73-110</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B45" t="inlineStr">
+        <x:is>
+          <x:t>Stargard</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C45" t="inlineStr">
+        <x:is>
+          <x:t>Plac Świętego Ducha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D45" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E45" t="inlineStr">
+        <x:is>
+          <x:t>Stargard</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F45" t="inlineStr">
+        <x:is>
+          <x:t>stargardzki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G45" t="inlineStr">
+        <x:is>
+          <x:t>zachodniopomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H45" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="inlineStr">
+        <x:is>
+          <x:t>70-895</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B46" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C46" t="inlineStr">
+        <x:is>
+          <x:t>pl. plac św. Dzieci Fatimskich</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D46" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E46" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F46" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G46" t="inlineStr">
+        <x:is>
+          <x:t>zachodniopomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H46" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="inlineStr">
+        <x:is>
+          <x:t>70-895</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B47" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C47" t="inlineStr">
+        <x:is>
+          <x:t>pl. plac św. Dzieci Fatimskich</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D47" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E47" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F47" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G47" t="inlineStr">
+        <x:is>
+          <x:t>zachodniopomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H47" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="inlineStr">
+        <x:is>
+          <x:t>71-602</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B48" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C48" t="inlineStr">
+        <x:is>
+          <x:t>Storrady-Świętosławy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D48" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E48" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F48" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G48" t="inlineStr">
+        <x:is>
+          <x:t>zachodniopomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H48" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="inlineStr">
+        <x:is>
+          <x:t>71-602</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B49" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C49" t="inlineStr">
+        <x:is>
+          <x:t>Storrady-Świętosławy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D49" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E49" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F49" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G49" t="inlineStr">
+        <x:is>
+          <x:t>zachodniopomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H49" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="inlineStr">
+        <x:is>
+          <x:t>70-205</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B50" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C50" t="inlineStr">
+        <x:is>
+          <x:t>Świętego Ducha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D50" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E50" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F50" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G50" t="inlineStr">
+        <x:is>
+          <x:t>zachodniopomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H50" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="inlineStr">
+        <x:is>
+          <x:t>70-205</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B51" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C51" t="inlineStr">
+        <x:is>
+          <x:t>Świętego Ducha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D51" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E51" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F51" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G51" t="inlineStr">
+        <x:is>
+          <x:t>zachodniopomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H51" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="inlineStr">
+        <x:is>
+          <x:t>33-100</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B52" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C52" t="inlineStr">
+        <x:is>
+          <x:t>świętego Ducha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D52" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E52" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F52" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G52" t="inlineStr">
+        <x:is>
+          <x:t>małopolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H52" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="inlineStr">
+        <x:is>
+          <x:t>33-100</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B53" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C53" t="inlineStr">
+        <x:is>
+          <x:t>świętego Ducha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D53" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E53" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F53" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G53" t="inlineStr">
+        <x:is>
+          <x:t>małopolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H53" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="inlineStr">
+        <x:is>
+          <x:t>33-100</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B54" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C54" t="inlineStr">
+        <x:is>
+          <x:t>Świętej Trójcy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D54" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E54" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F54" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G54" t="inlineStr">
+        <x:is>
+          <x:t>małopolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H54" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="inlineStr">
+        <x:is>
+          <x:t>33-100</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B55" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C55" t="inlineStr">
+        <x:is>
+          <x:t>Świętej Trójcy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D55" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E55" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F55" t="inlineStr">
+        <x:is>
+          <x:t>Tarnów</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G55" t="inlineStr">
+        <x:is>
+          <x:t>małopolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H55" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="inlineStr">
+        <x:is>
+          <x:t>02-495</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B56" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C56" t="inlineStr">
+        <x:is>
+          <x:t>Świętej Rodziny</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D56" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E56" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F56" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G56" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H56" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="inlineStr">
+        <x:is>
+          <x:t>02-495</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B57" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C57" t="inlineStr">
+        <x:is>
+          <x:t>Świętej Rodziny</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D57" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E57" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F57" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G57" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H57" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="inlineStr">
+        <x:is>
+          <x:t>44-300</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58" t="inlineStr">
+        <x:is>
+          <x:t>Wodzisław Śląski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C58" t="inlineStr">
+        <x:is>
+          <x:t>Plac Świętego Krzyża</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D58" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E58" t="inlineStr">
+        <x:is>
+          <x:t>Wodzisław Śląski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F58" t="inlineStr">
+        <x:is>
+          <x:t>wodzisławski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G58" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H58" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="inlineStr">
+        <x:is>
+          <x:t>44-300</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B59" t="inlineStr">
+        <x:is>
+          <x:t>Wodzisław Śląski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C59" t="inlineStr">
+        <x:is>
+          <x:t>Plac Świętego Krzyża</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D59" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E59" t="inlineStr">
+        <x:is>
+          <x:t>Wodzisław Śląski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F59" t="inlineStr">
+        <x:is>
+          <x:t>wodzisławski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G59" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H59" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="inlineStr">
+        <x:is>
+          <x:t>50-153</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B60" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C60" t="inlineStr">
+        <x:is>
+          <x:t>św. Ducha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D60" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E60" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F60" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G60" t="inlineStr">
+        <x:is>
+          <x:t>dolnośląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H60" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="inlineStr">
+        <x:is>
+          <x:t>50-153</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B61" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C61" t="inlineStr">
+        <x:is>
+          <x:t>św. Ducha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D61" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E61" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F61" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G61" t="inlineStr">
+        <x:is>
+          <x:t>dolnośląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H61" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="inlineStr">
+        <x:is>
+          <x:t>53-604</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B62" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C62" t="inlineStr">
+        <x:is>
+          <x:t>św. Trójcy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D62" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E62" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F62" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G62" t="inlineStr">
+        <x:is>
+          <x:t>dolnośląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H62" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="inlineStr">
+        <x:is>
+          <x:t>53-604</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B63" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C63" t="inlineStr">
+        <x:is>
+          <x:t>św. Trójcy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D63" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E63" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F63" t="inlineStr">
+        <x:is>
+          <x:t>Wrocław</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G63" t="inlineStr">
+        <x:is>
+          <x:t>dolnośląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H63" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="inlineStr">
+        <x:is>
+          <x:t>07-200</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B64" t="inlineStr">
+        <x:is>
+          <x:t>Wyszków</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C64" t="inlineStr">
+        <x:is>
+          <x:t>Świętej Rodziny</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D64" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E64" t="inlineStr">
+        <x:is>
+          <x:t>Wyszków</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F64" t="inlineStr">
+        <x:is>
+          <x:t>wyszkowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G64" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H64" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="inlineStr">
+        <x:is>
+          <x:t>07-200</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B65" t="inlineStr">
+        <x:is>
+          <x:t>Wyszków</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C65" t="inlineStr">
+        <x:is>
+          <x:t>Świętej Rodziny</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D65" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E65" t="inlineStr">
+        <x:is>
+          <x:t>Wyszków</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F65" t="inlineStr">
+        <x:is>
+          <x:t>wyszkowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G65" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H65" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="inlineStr">
+        <x:is>
+          <x:t>65-097</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66" t="inlineStr">
+        <x:is>
           <x:t>Zielona Góra</x:t>
         </x:is>
       </x:c>
-      <x:c r="C29" t="inlineStr">
-        <x:is>
-          <x:t>Ochla-Osiedle Dworskie</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D29" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="E29" t="inlineStr">
+      <x:c r="C66" t="inlineStr">
+        <x:is>
+          <x:t>św. Trójcy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D66" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E66" t="inlineStr">
         <x:is>
           <x:t>Zielona Góra</x:t>
         </x:is>
       </x:c>
-      <x:c r="F29" t="inlineStr">
+      <x:c r="F66" t="inlineStr">
         <x:is>
           <x:t>Zielona Góra</x:t>
         </x:is>
       </x:c>
-      <x:c r="G29" t="inlineStr">
+      <x:c r="G66" t="inlineStr">
         <x:is>
           <x:t>lubuskie</x:t>
         </x:is>
       </x:c>
-      <x:c r="H29" t="inlineStr">
+      <x:c r="H66" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="inlineStr">
+        <x:is>
+          <x:t>65-097</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B67" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C67" t="inlineStr">
+        <x:is>
+          <x:t>św. Trójcy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D67" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E67" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F67" t="inlineStr">
+        <x:is>
+          <x:t>Zielona Góra</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G67" t="inlineStr">
+        <x:is>
+          <x:t>lubuskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H67" t="inlineStr">
         <x:is>
           <x:t/>
         </x:is>

--- a/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
+++ b/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="Rcc5879e76cc242da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="R009ac3357fa44915"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,17 +139,17 @@
     <x:row r="4">
       <x:c r="A4" t="inlineStr">
         <x:is>
-          <x:t>31-812</x:t>
+          <x:t>48-300</x:t>
         </x:is>
       </x:c>
       <x:c r="B4" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>Nysa</x:t>
         </x:is>
       </x:c>
       <x:c r="C4" t="inlineStr">
         <x:is>
-          <x:t>Świętej Rodziny</x:t>
+          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr">
@@ -159,17 +159,17 @@
       </x:c>
       <x:c r="E4" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>Nysa</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>nyski</x:t>
         </x:is>
       </x:c>
       <x:c r="G4" t="inlineStr">
         <x:is>
-          <x:t>małopolskie</x:t>
+          <x:t>opolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr">
@@ -181,17 +181,17 @@
     <x:row r="5">
       <x:c r="A5" t="inlineStr">
         <x:is>
-          <x:t>31-812</x:t>
+          <x:t>48-300</x:t>
         </x:is>
       </x:c>
       <x:c r="B5" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>Nysa</x:t>
         </x:is>
       </x:c>
       <x:c r="C5" t="inlineStr">
         <x:is>
-          <x:t>Świętej Rodziny</x:t>
+          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr">
@@ -201,17 +201,17 @@
       </x:c>
       <x:c r="E5" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>Nysa</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" t="inlineStr">
         <x:is>
-          <x:t>Kraków</x:t>
+          <x:t>nyski</x:t>
         </x:is>
       </x:c>
       <x:c r="G5" t="inlineStr">
         <x:is>
-          <x:t>małopolskie</x:t>
+          <x:t>opolskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr">
@@ -223,17 +223,17 @@
     <x:row r="6">
       <x:c r="A6" t="inlineStr">
         <x:is>
-          <x:t>48-300</x:t>
+          <x:t>42-256</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Olsztyn</x:t>
         </x:is>
       </x:c>
       <x:c r="C6" t="inlineStr">
         <x:is>
-          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr">
@@ -243,17 +243,17 @@
       </x:c>
       <x:c r="E6" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Olsztyn</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" t="inlineStr">
         <x:is>
-          <x:t>nyski</x:t>
+          <x:t>częstochowski</x:t>
         </x:is>
       </x:c>
       <x:c r="G6" t="inlineStr">
         <x:is>
-          <x:t>opolskie</x:t>
+          <x:t>śląskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr">
@@ -265,17 +265,17 @@
     <x:row r="7">
       <x:c r="A7" t="inlineStr">
         <x:is>
-          <x:t>48-300</x:t>
+          <x:t>42-256</x:t>
         </x:is>
       </x:c>
       <x:c r="B7" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Olsztyn</x:t>
         </x:is>
       </x:c>
       <x:c r="C7" t="inlineStr">
         <x:is>
-          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr">
@@ -285,17 +285,17 @@
       </x:c>
       <x:c r="E7" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Olsztyn</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" t="inlineStr">
         <x:is>
-          <x:t>nyski</x:t>
+          <x:t>częstochowski</x:t>
         </x:is>
       </x:c>
       <x:c r="G7" t="inlineStr">
         <x:is>
-          <x:t>opolskie</x:t>
+          <x:t>śląskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr">
@@ -307,17 +307,17 @@
     <x:row r="8">
       <x:c r="A8" t="inlineStr">
         <x:is>
-          <x:t>42-256</x:t>
+          <x:t>07-310</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Ostrów Mazowiecka</x:t>
         </x:is>
       </x:c>
       <x:c r="C8" t="inlineStr">
         <x:is>
-          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+          <x:t>Spokojna</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr">
@@ -327,17 +327,17 @@
       </x:c>
       <x:c r="E8" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Ostrów Mazowiecka</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" t="inlineStr">
         <x:is>
-          <x:t>częstochowski</x:t>
+          <x:t>ostrowski</x:t>
         </x:is>
       </x:c>
       <x:c r="G8" t="inlineStr">
         <x:is>
-          <x:t>śląskie</x:t>
+          <x:t>mazowieckie</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr">
@@ -349,17 +349,17 @@
     <x:row r="9">
       <x:c r="A9" t="inlineStr">
         <x:is>
-          <x:t>42-256</x:t>
+          <x:t>07-310</x:t>
         </x:is>
       </x:c>
       <x:c r="B9" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Ostrów Mazowiecka</x:t>
         </x:is>
       </x:c>
       <x:c r="C9" t="inlineStr">
         <x:is>
-          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+          <x:t>Spokojna</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr">
@@ -369,17 +369,17 @@
       </x:c>
       <x:c r="E9" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Ostrów Mazowiecka</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" t="inlineStr">
         <x:is>
-          <x:t>częstochowski</x:t>
+          <x:t>ostrowski</x:t>
         </x:is>
       </x:c>
       <x:c r="G9" t="inlineStr">
         <x:is>
-          <x:t>śląskie</x:t>
+          <x:t>mazowieckie</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr">
@@ -391,17 +391,17 @@
     <x:row r="10">
       <x:c r="A10" t="inlineStr">
         <x:is>
-          <x:t>07-310</x:t>
+          <x:t>71-602</x:t>
         </x:is>
       </x:c>
       <x:c r="B10" t="inlineStr">
         <x:is>
-          <x:t>Ostrów Mazowiecka</x:t>
+          <x:t>Szczecin</x:t>
         </x:is>
       </x:c>
       <x:c r="C10" t="inlineStr">
         <x:is>
-          <x:t>Spokojna</x:t>
+          <x:t>Storrady-Świętosławy</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr">
@@ -411,17 +411,17 @@
       </x:c>
       <x:c r="E10" t="inlineStr">
         <x:is>
-          <x:t>Ostrów Mazowiecka</x:t>
+          <x:t>Szczecin</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" t="inlineStr">
         <x:is>
-          <x:t>ostrowski</x:t>
+          <x:t>Szczecin</x:t>
         </x:is>
       </x:c>
       <x:c r="G10" t="inlineStr">
         <x:is>
-          <x:t>mazowieckie</x:t>
+          <x:t>zachodniopomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr">
@@ -433,17 +433,17 @@
     <x:row r="11">
       <x:c r="A11" t="inlineStr">
         <x:is>
-          <x:t>07-310</x:t>
+          <x:t>71-602</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" t="inlineStr">
         <x:is>
-          <x:t>Ostrów Mazowiecka</x:t>
+          <x:t>Szczecin</x:t>
         </x:is>
       </x:c>
       <x:c r="C11" t="inlineStr">
         <x:is>
-          <x:t>Spokojna</x:t>
+          <x:t>Storrady-Świętosławy</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr">
@@ -453,356 +453,20 @@
       </x:c>
       <x:c r="E11" t="inlineStr">
         <x:is>
-          <x:t>Ostrów Mazowiecka</x:t>
+          <x:t>Szczecin</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" t="inlineStr">
         <x:is>
-          <x:t>ostrowski</x:t>
+          <x:t>Szczecin</x:t>
         </x:is>
       </x:c>
       <x:c r="G11" t="inlineStr">
         <x:is>
-          <x:t>mazowieckie</x:t>
+          <x:t>zachodniopomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="inlineStr">
-        <x:is>
-          <x:t>35-213</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" t="inlineStr">
-        <x:is>
-          <x:t>Rzeszów</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" t="inlineStr">
-        <x:is>
-          <x:t>Świętej Rodziny</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="E12" t="inlineStr">
-        <x:is>
-          <x:t>Rzeszów</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" t="inlineStr">
-        <x:is>
-          <x:t>Rzeszów</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" t="inlineStr">
-        <x:is>
-          <x:t>podkarpackie</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" t="inlineStr">
-        <x:is>
-          <x:t>Brak ulicy</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="inlineStr">
-        <x:is>
-          <x:t>35-213</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" t="inlineStr">
-        <x:is>
-          <x:t>Rzeszów</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" t="inlineStr">
-        <x:is>
-          <x:t>Świętej Rodziny</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="E13" t="inlineStr">
-        <x:is>
-          <x:t>Rzeszów</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" t="inlineStr">
-        <x:is>
-          <x:t>Rzeszów</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G13" t="inlineStr">
-        <x:is>
-          <x:t>podkarpackie</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="inlineStr">
-        <x:is>
-          <x:t>71-602</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" t="inlineStr">
-        <x:is>
-          <x:t>Szczecin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" t="inlineStr">
-        <x:is>
-          <x:t>Storrady-Świętosławy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="E14" t="inlineStr">
-        <x:is>
-          <x:t>Szczecin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" t="inlineStr">
-        <x:is>
-          <x:t>Szczecin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G14" t="inlineStr">
-        <x:is>
-          <x:t>zachodniopomorskie</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" t="inlineStr">
-        <x:is>
-          <x:t>Brak ulicy</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="inlineStr">
-        <x:is>
-          <x:t>71-602</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" t="inlineStr">
-        <x:is>
-          <x:t>Szczecin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" t="inlineStr">
-        <x:is>
-          <x:t>Storrady-Świętosławy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="E15" t="inlineStr">
-        <x:is>
-          <x:t>Szczecin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" t="inlineStr">
-        <x:is>
-          <x:t>Szczecin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G15" t="inlineStr">
-        <x:is>
-          <x:t>zachodniopomorskie</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="inlineStr">
-        <x:is>
-          <x:t>02-495</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" t="inlineStr">
-        <x:is>
-          <x:t>Warszawa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" t="inlineStr">
-        <x:is>
-          <x:t>Świętej Rodziny</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="E16" t="inlineStr">
-        <x:is>
-          <x:t>Warszawa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" t="inlineStr">
-        <x:is>
-          <x:t>Warszawa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" t="inlineStr">
-        <x:is>
-          <x:t>mazowieckie</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" t="inlineStr">
-        <x:is>
-          <x:t>Brak ulicy</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="inlineStr">
-        <x:is>
-          <x:t>02-495</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" t="inlineStr">
-        <x:is>
-          <x:t>Warszawa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" t="inlineStr">
-        <x:is>
-          <x:t>Świętej Rodziny</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="E17" t="inlineStr">
-        <x:is>
-          <x:t>Warszawa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" t="inlineStr">
-        <x:is>
-          <x:t>Warszawa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G17" t="inlineStr">
-        <x:is>
-          <x:t>mazowieckie</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H17" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="inlineStr">
-        <x:is>
-          <x:t>07-200</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" t="inlineStr">
-        <x:is>
-          <x:t>Wyszków</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" t="inlineStr">
-        <x:is>
-          <x:t>Świętej Rodziny</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="E18" t="inlineStr">
-        <x:is>
-          <x:t>Wyszków</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" t="inlineStr">
-        <x:is>
-          <x:t>wyszkowski</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G18" t="inlineStr">
-        <x:is>
-          <x:t>mazowieckie</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" t="inlineStr">
-        <x:is>
-          <x:t>Brak ulicy</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="inlineStr">
-        <x:is>
-          <x:t>07-200</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" t="inlineStr">
-        <x:is>
-          <x:t>Wyszków</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" t="inlineStr">
-        <x:is>
-          <x:t>Świętej Rodziny</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="E19" t="inlineStr">
-        <x:is>
-          <x:t>Wyszków</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" t="inlineStr">
-        <x:is>
-          <x:t>wyszkowski</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G19" t="inlineStr">
-        <x:is>
-          <x:t>mazowieckie</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" t="inlineStr">
         <x:is>
           <x:t/>
         </x:is>

--- a/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
+++ b/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="R009ac3357fa44915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="Rab979c9e76144726"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
+++ b/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="Rab979c9e76144726"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="Rac0aa5e259ca423c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,17 +139,17 @@
     <x:row r="4">
       <x:c r="A4" t="inlineStr">
         <x:is>
-          <x:t>48-300</x:t>
+          <x:t>15-568</x:t>
         </x:is>
       </x:c>
       <x:c r="B4" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="C4" t="inlineStr">
         <x:is>
-          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+          <x:t>św. Proroka Eliasza</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr">
@@ -159,17 +159,17 @@
       </x:c>
       <x:c r="E4" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" t="inlineStr">
         <x:is>
-          <x:t>nyski</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="G4" t="inlineStr">
         <x:is>
-          <x:t>opolskie</x:t>
+          <x:t>podlaskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr">
@@ -181,17 +181,17 @@
     <x:row r="5">
       <x:c r="A5" t="inlineStr">
         <x:is>
-          <x:t>48-300</x:t>
+          <x:t>15-568</x:t>
         </x:is>
       </x:c>
       <x:c r="B5" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="C5" t="inlineStr">
         <x:is>
-          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+          <x:t>św. Proroka Eliasza</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr">
@@ -201,17 +201,17 @@
       </x:c>
       <x:c r="E5" t="inlineStr">
         <x:is>
-          <x:t>Nysa</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" t="inlineStr">
         <x:is>
-          <x:t>nyski</x:t>
+          <x:t>Białystok</x:t>
         </x:is>
       </x:c>
       <x:c r="G5" t="inlineStr">
         <x:is>
-          <x:t>opolskie</x:t>
+          <x:t>podlaskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr">
@@ -223,17 +223,17 @@
     <x:row r="6">
       <x:c r="A6" t="inlineStr">
         <x:is>
-          <x:t>42-256</x:t>
+          <x:t>85-791</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="C6" t="inlineStr">
         <x:is>
-          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+          <x:t>pl. plac św. Mateusza Apostoła i Ewangelisty</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr">
@@ -243,17 +243,17 @@
       </x:c>
       <x:c r="E6" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" t="inlineStr">
         <x:is>
-          <x:t>częstochowski</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="G6" t="inlineStr">
         <x:is>
-          <x:t>śląskie</x:t>
+          <x:t>kujawsko-pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr">
@@ -265,17 +265,17 @@
     <x:row r="7">
       <x:c r="A7" t="inlineStr">
         <x:is>
-          <x:t>42-256</x:t>
+          <x:t>85-791</x:t>
         </x:is>
       </x:c>
       <x:c r="B7" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="C7" t="inlineStr">
         <x:is>
-          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+          <x:t>pl. plac św. Mateusza Apostoła i Ewangelisty</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr">
@@ -285,17 +285,17 @@
       </x:c>
       <x:c r="E7" t="inlineStr">
         <x:is>
-          <x:t>Olsztyn</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" t="inlineStr">
         <x:is>
-          <x:t>częstochowski</x:t>
+          <x:t>Bydgoszcz</x:t>
         </x:is>
       </x:c>
       <x:c r="G7" t="inlineStr">
         <x:is>
-          <x:t>śląskie</x:t>
+          <x:t>kujawsko-pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr">
@@ -307,17 +307,17 @@
     <x:row r="8">
       <x:c r="A8" t="inlineStr">
         <x:is>
-          <x:t>07-310</x:t>
+          <x:t>80-893</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" t="inlineStr">
         <x:is>
-          <x:t>Ostrów Mazowiecka</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="C8" t="inlineStr">
         <x:is>
-          <x:t>Spokojna</x:t>
+          <x:t>Bastion św. Elżbiety</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr">
@@ -327,17 +327,17 @@
       </x:c>
       <x:c r="E8" t="inlineStr">
         <x:is>
-          <x:t>Ostrów Mazowiecka</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" t="inlineStr">
         <x:is>
-          <x:t>ostrowski</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="G8" t="inlineStr">
         <x:is>
-          <x:t>mazowieckie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr">
@@ -349,17 +349,17 @@
     <x:row r="9">
       <x:c r="A9" t="inlineStr">
         <x:is>
-          <x:t>07-310</x:t>
+          <x:t>80-893</x:t>
         </x:is>
       </x:c>
       <x:c r="B9" t="inlineStr">
         <x:is>
-          <x:t>Ostrów Mazowiecka</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="C9" t="inlineStr">
         <x:is>
-          <x:t>Spokojna</x:t>
+          <x:t>Bastion św. Elżbiety</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr">
@@ -369,17 +369,17 @@
       </x:c>
       <x:c r="E9" t="inlineStr">
         <x:is>
-          <x:t>Ostrów Mazowiecka</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" t="inlineStr">
         <x:is>
-          <x:t>ostrowski</x:t>
+          <x:t>Gdańsk</x:t>
         </x:is>
       </x:c>
       <x:c r="G9" t="inlineStr">
         <x:is>
-          <x:t>mazowieckie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr">
@@ -391,17 +391,17 @@
     <x:row r="10">
       <x:c r="A10" t="inlineStr">
         <x:is>
-          <x:t>71-602</x:t>
+          <x:t>81-402</x:t>
         </x:is>
       </x:c>
       <x:c r="B10" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Gdynia</x:t>
         </x:is>
       </x:c>
       <x:c r="C10" t="inlineStr">
         <x:is>
-          <x:t>Storrady-Świętosławy</x:t>
+          <x:t>bp. Dominika</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr">
@@ -411,17 +411,17 @@
       </x:c>
       <x:c r="E10" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Gdynia</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" t="inlineStr">
         <x:is>
-          <x:t>Szczecin</x:t>
+          <x:t>Gdynia</x:t>
         </x:is>
       </x:c>
       <x:c r="G10" t="inlineStr">
         <x:is>
-          <x:t>zachodniopomorskie</x:t>
+          <x:t>pomorskie</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr">
@@ -433,40 +433,628 @@
     <x:row r="11">
       <x:c r="A11" t="inlineStr">
         <x:is>
+          <x:t>81-402</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" t="inlineStr">
+        <x:is>
+          <x:t>Gdynia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" t="inlineStr">
+        <x:is>
+          <x:t>bp. Dominika</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E11" t="inlineStr">
+        <x:is>
+          <x:t>Gdynia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" t="inlineStr">
+        <x:is>
+          <x:t>Gdynia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" t="inlineStr">
+        <x:is>
+          <x:t>pomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H11" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="inlineStr">
+        <x:is>
+          <x:t>48-300</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" t="inlineStr">
+        <x:is>
+          <x:t>Nysa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" t="inlineStr">
+        <x:is>
+          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E12" t="inlineStr">
+        <x:is>
+          <x:t>Nysa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" t="inlineStr">
+        <x:is>
+          <x:t>nyski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G12" t="inlineStr">
+        <x:is>
+          <x:t>opolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H12" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="inlineStr">
+        <x:is>
+          <x:t>48-300</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" t="inlineStr">
+        <x:is>
+          <x:t>Nysa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" t="inlineStr">
+        <x:is>
+          <x:t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E13" t="inlineStr">
+        <x:is>
+          <x:t>Nysa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" t="inlineStr">
+        <x:is>
+          <x:t>nyski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G13" t="inlineStr">
+        <x:is>
+          <x:t>opolskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H13" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="inlineStr">
+        <x:is>
+          <x:t>42-256</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" t="inlineStr">
+        <x:is>
+          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E14" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" t="inlineStr">
+        <x:is>
+          <x:t>częstochowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G14" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H14" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="inlineStr">
+        <x:is>
+          <x:t>42-256</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" t="inlineStr">
+        <x:is>
+          <x:t>Plac im. marszałka Józefa Piłsudskiego</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E15" t="inlineStr">
+        <x:is>
+          <x:t>Olsztyn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" t="inlineStr">
+        <x:is>
+          <x:t>częstochowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G15" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H15" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="inlineStr">
+        <x:is>
+          <x:t>07-310</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" t="inlineStr">
+        <x:is>
+          <x:t>Ostrów Mazowiecka</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" t="inlineStr">
+        <x:is>
+          <x:t>Spokojna</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E16" t="inlineStr">
+        <x:is>
+          <x:t>Ostrów Mazowiecka</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" t="inlineStr">
+        <x:is>
+          <x:t>ostrowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G16" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H16" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="inlineStr">
+        <x:is>
+          <x:t>07-310</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" t="inlineStr">
+        <x:is>
+          <x:t>Ostrów Mazowiecka</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" t="inlineStr">
+        <x:is>
+          <x:t>Spokojna</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E17" t="inlineStr">
+        <x:is>
+          <x:t>Ostrów Mazowiecka</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" t="inlineStr">
+        <x:is>
+          <x:t>ostrowski</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G17" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H17" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="inlineStr">
+        <x:is>
+          <x:t>41-711</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" t="inlineStr">
+        <x:is>
+          <x:t>Ruda Śląska</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" t="inlineStr">
+        <x:is>
+          <x:t>Dr. Jordana</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E18" t="inlineStr">
+        <x:is>
+          <x:t>Ruda Śląska</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F18" t="inlineStr">
+        <x:is>
+          <x:t>Ruda Śląska</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G18" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H18" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="inlineStr">
+        <x:is>
+          <x:t>41-711</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" t="inlineStr">
+        <x:is>
+          <x:t>Ruda Śląska</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" t="inlineStr">
+        <x:is>
+          <x:t>Dr. Jordana</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E19" t="inlineStr">
+        <x:is>
+          <x:t>Ruda Śląska</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F19" t="inlineStr">
+        <x:is>
+          <x:t>Ruda Śląska</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G19" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H19" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="inlineStr">
+        <x:is>
           <x:t>71-602</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" t="inlineStr">
+      <x:c r="B20" t="inlineStr">
         <x:is>
           <x:t>Szczecin</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" t="inlineStr">
+      <x:c r="C20" t="inlineStr">
         <x:is>
           <x:t>Storrady-Świętosławy</x:t>
         </x:is>
       </x:c>
-      <x:c r="D11" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="E11" t="inlineStr">
+      <x:c r="D20" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E20" t="inlineStr">
         <x:is>
           <x:t>Szczecin</x:t>
         </x:is>
       </x:c>
-      <x:c r="F11" t="inlineStr">
+      <x:c r="F20" t="inlineStr">
         <x:is>
           <x:t>Szczecin</x:t>
         </x:is>
       </x:c>
-      <x:c r="G11" t="inlineStr">
+      <x:c r="G20" t="inlineStr">
         <x:is>
           <x:t>zachodniopomorskie</x:t>
         </x:is>
       </x:c>
-      <x:c r="H11" t="inlineStr">
+      <x:c r="H20" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="inlineStr">
+        <x:is>
+          <x:t>71-602</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" t="inlineStr">
+        <x:is>
+          <x:t>Storrady-Świętosławy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E21" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F21" t="inlineStr">
+        <x:is>
+          <x:t>Szczecin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G21" t="inlineStr">
+        <x:is>
+          <x:t>zachodniopomorskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H21" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="inlineStr">
+        <x:is>
+          <x:t>02-647</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" t="inlineStr">
+        <x:is>
+          <x:t>Rabindranatha Tagore</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E22" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F22" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G22" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H22" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="inlineStr">
+        <x:is>
+          <x:t>02-647</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" t="inlineStr">
+        <x:is>
+          <x:t>Rabindranatha Tagore</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E23" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F23" t="inlineStr">
+        <x:is>
+          <x:t>Warszawa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G23" t="inlineStr">
+        <x:is>
+          <x:t>mazowieckie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H23" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="inlineStr">
+        <x:is>
+          <x:t>41-800</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" t="inlineStr">
+        <x:is>
+          <x:t>Zabrze</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" t="inlineStr">
+        <x:is>
+          <x:t>Góry św. Anny</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E24" t="inlineStr">
+        <x:is>
+          <x:t>Zabrze</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F24" t="inlineStr">
+        <x:is>
+          <x:t>Zabrze</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G24" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H24" t="inlineStr">
+        <x:is>
+          <x:t>Brak ulicy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="inlineStr">
+        <x:is>
+          <x:t>41-800</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" t="inlineStr">
+        <x:is>
+          <x:t>Zabrze</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" t="inlineStr">
+        <x:is>
+          <x:t>Góry św. Anny</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D25" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="E25" t="inlineStr">
+        <x:is>
+          <x:t>Zabrze</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F25" t="inlineStr">
+        <x:is>
+          <x:t>Zabrze</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G25" t="inlineStr">
+        <x:is>
+          <x:t>śląskie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H25" t="inlineStr">
         <x:is>
           <x:t/>
         </x:is>

--- a/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
+++ b/TerytLoad/AppData/pna/BledyPnaPropozycje.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="Rb5713f811dc242c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Błędy PNA" sheetId="1" r:id="R15d2ea9399104b0a"/>
   </x:sheets>
 </x:workbook>
 </file>
